--- a/output/第10期計画_追加調査報告書.xlsx
+++ b/output/第10期計画_追加調査報告書.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_北海道の指標の読替え" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_事業所ゼロのサービス" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_人口推計の補正方法" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_原典確認による訂正" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -123,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -142,20 +143,29 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -522,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -591,12 +601,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>「中山間地域」には3つの異なる制度上の概念があり、区別が必要。①介護報酬上の中山間地域等（豪雪地帯等）＝北海道は179市町村すべてが豪雪地帯のため3町とも該当。②特別地域加算の対象地域＝別の狭い告示による。3町の該当は要確認。③第10期基本指針の「中山間・人口減少地域」＝新設される「特定地域」。基準素案は75歳以上人口が1km²あたり5人未満又は1,000人未満かつ減少。これを3町に当てはめると、美瑛町は該当が確実、東神楽町は非該当が確実、東川町は非該当だが要確認。保険者単位ではなく市町村単位で判定されるため、広域連合内で適用が分かれる。</t>
+          <t>3町の地域指定が原典で確定した（北海道 地域指定一覧 令和8年4月1日現在）。美瑛町＝過疎・辺地・特別豪雪地帯、東川町＝辺地・特別豪雪地帯、東神楽町＝辺地。豪雪地帯は道内全市町村。したがって3町とも介護報酬上の中山間地域等に該当する。特定地域（中山間・人口減少地域）の基準は3段階構造であることが原典で判明した。①特別地域加算・離島等相当サービスの対象地域は無条件で含まれる（全部指定・一部指定とも）。②これに該当しない市町村は「75歳以上人口密度5人／km²未満」又は「75歳以上人口1,000人未満かつ減少」で全域指定できる。③①②に該当しない場合でも、市町村内の一部地域が②の基準に該当する地域や、特定のサービス類型の事業所が地域に存在しない地域を指定できる。③により、当広域連合は3町とも指定の道が開かれている（前回報告からの重要な訂正）。</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>基準は報道・二次資料による。原典（第135回資料3）は未確認</t>
+          <t>原典（第135回資料3・北海道地域指定一覧）で確認済み</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr"/>
@@ -615,12 +625,12 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>評価と公表は介護保険法第117条に基づく法定事項で、第7期から評価項目が法定化されている。市町村は自己評価を都道府県へ報告するとともに、公表に努めることとされている。厚生労働省は「介護保険事業（支援）計画の進捗管理の手引き」（平成30年7月30日）を示している。他団体では、自己評価結果のホームページ掲載（広島県府中町）、KPIの実績値・目標値の年次管理（大阪府堺市ほか）、交付金評価指数が全国平均を上回る市町村数を都道府県KPIとする例（島根県）がある。当広域連合の0点は、取組の有無ではなく「共有の場と記録がない」ことに起因する可能性が高い。</t>
+          <t>厚生労働省「介護保険事業（支援）計画の進捗管理の手引き」（平成30年7月30日）に標準的な手順が示されている。同手引きは、3年ごとのPDCAだけでなく年度ごとのPDCAを回すべきとし、①前年度実績（6月頃確定）による自己評価と、②9月末現在の中間実績による10月の自己評価、の2つのサイクルを同時に活用することを求めている。様式として「取組と目標に対する自己評価シート」（フェイスシート＋各年度の自己評価結果）が示されており、広島県府中町はこの様式のまま令和6年度分を作成・公表している。府中町は法定2区分（自立支援等／給付適正化）ごとに1件ずつ作成し、給付適正化では認定調査の適正化・ケアプラン点検・縦覧点検と医療情報との突合・事業者指導の4本立てで目標と実績を記載している。当広域連合が0点である項目は、まさに府中町が実施している内容である。</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>法的根拠は確実。他団体事例は検索結果による</t>
+          <t>原典（進捗管理の手引き・府中町自己評価シート）で確認済み</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr"/>
@@ -639,12 +649,12 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>基本指針案は判定基準を示していない。実務上の判定材料は、①各事業所の運営規程に定める「通常の事業の実施地域」に含まれるか、②中山間地域等居住者サービス提供加算の算定実績があるか、③公共交通の状況、④冬期の道路状況、の4点。美瑛町の朗根内地区（人口233人）は鉄道駅・定期路線バスがなく、該当の可能性が高い。美馬牛地区はJR富良野線美馬牛駅があり、旭・北西地区は高齢化率45.0％だが交通は要確認。確定には3町の指定台帳から「通常の事業の実施地域」を抽出する必要がある。</t>
+          <t>美瑛町過疎地域持続的発展市町村計画により、決定的な事実が確認できた。①国鉄バスの路線廃止により昭和60年から代替のスクールバスが運行されており、現在10路線。同計画は「高齢者の通院や日常の買い物など交通弱者の貴重な公共交通として、スクールバスは欠くことのできない交通手段」と明記している。すなわち朗根内地区を含む集落には定期路線バスがない。②俵真布線（美瑛〜朗根内〜俵真布）の乗車人員は令和2年度8,188人で10路線中最多であり、同地区の交通需要は大きい。③町道414路線346.6kmの除雪率は52.9％で、目標60％に達していない。冬期に除雪されない町道が約半分ある。これらは訪問・通所困難地域の該当性を強く裏付ける。確定には各事業所の「通常の事業の実施地域」の収集を要する。</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>判定材料の枠組みは確実。個別判定は要データ</t>
+          <t>原典（美瑛町過疎地域持続的発展市町村計画）で確認済み</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr"/>
@@ -687,12 +697,12 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>受領した「自然体推計の計算過程確認シートのガイド」に公式の手順が明記されている。実績値がないサービスは自然体推計がゼロとなるため、整備予定がある場合は利用者数を施策反映値として直接入力し、給付費は整備計画又は全国平均値等を参考に「※推計に利用する給付費」へ直接入力する。国は令和9年4月から「特定地域サービス」（人員基準緩和・包括払い）と「特定地域居宅サービス等事業」（サービス提供主体が少ない場合に市町村が事業として実施）を創設する方針であり、当広域連合の11種別の空白に直接対応する制度である。</t>
+          <t>推計上の手順は「自然体推計の計算過程確認シートのガイド」に明記されている。実績値がないサービスは自然体推計がゼロとなるため、整備予定がある場合は利用者数を施策反映値として直接入力し、給付費は整備計画又は全国平均値等を参考に「※推計に利用する給付費」へ直接入力する。制度面では、第135回資料3により、特定地域の基準③(2)が「特定のサービス類型の事業所が地域に存在しない…など、現に指定サービス等を前提としたサービス基盤の維持が困難である地域」を指定対象として明記していることが確認できた。当広域連合の11種別の空白はこの規定に直接該当する。また特例介護サービスの新類型は、居宅サービス等に加え施設サービス・特定施設入居者生活介護・地域密着型サービスも対象とすることが適当とされている。</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>推計手順は原典で確認済み。新制度は報道・二次資料による</t>
+          <t>原典（第135回資料3・受領ガイド）で確認済み</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr"/>
@@ -753,7 +763,7 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>本セッションの外部HTTPS接続は組織のegressポリシーにより制限されており、厚生労働省（mhlw.go.jp）、北海道（pref.hokkaido.lg.jp）、3町の各サイト、ウィキペディアを含むすべてのサイトへの直接アクセス（ページ本文の取得）が403で拒否されました。検索エンジンの結果（見出しと要約）のみ取得できます。</t>
+          <t>本セッションの外部HTTPS接続は組織のegressポリシーにより制限されており、厚生労働省（mhlw.go.jp）、北海道（pref.hokkaido.lg.jp）、3町の各サイトを含むすべてのサイトへの直接アクセス（ページ本文の取得）が403で拒否されました。第1版は検索エンジンの結果（見出しと要約）に依拠していましたが、発注者から原典5点の提供を受け、第2版では全事項を原典で検証しています。</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr"/>
@@ -780,12 +790,12 @@
     <row r="17" ht="96" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>原典確認を要する事項</t>
+          <t>発注者から提供を受けた原典（令和8年7月29日）</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>①第135回社会保障審議会介護保険部会 資料3「特定地域（中山間・人口減少地域）の考え方について」（https://www.mhlw.go.jp/content/12300000/001715736.pdf）の基準の正確な文言。②厚生労働大臣が定める中山間地域等の地域（平成21年3月13日厚生労働省告示第83号）及び特別地域加算の対象地域告示における3町の記載の有無。③北海道『道内の過疎、辺地、山村、離島、特豪地帯等の指定状況（令和8年4月1日現在）』（https://www.pref.hokkaido.lg.jp/ss/ckk/74368.html）における3町の指定状況。④3町の面積及び年齢階級別人口の確定値。</t>
+          <t>①第135回社会保障審議会介護保険部会 資料3「特定地域（中山間・人口減少地域）の考え方について」（令和8年6月29日・34ページ）。②国土交通省「豪雪地帯・特別豪雪地帯の指定（令和8年4月1日現在）」。③北海道 総合政策部地域創生局地域政策課「地域指定一覧（令和8年4月1日現在）」。④厚生労働省老健局介護保険計画課「介護保険事業（支援）計画の進捗管理の手引き」（平成30年7月30日・34ページ）。⑤美瑛町過疎地域持続的発展市町村計画（令和3年度〜令和7年度・75ページ）。⑥広島県府中町「取組と目標に対する自己評価シート」（令和6年度分）。</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr"/>
@@ -793,8 +803,24 @@
       <c r="E17" s="6" t="inlineStr"/>
       <c r="F17" s="6" t="inlineStr"/>
     </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+    <row r="18" ht="96" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>なお確認を要する事項</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>①特別地域加算の対象地域告示（厚生労働大臣が定める特別地域）に3町が掲載されているかどうか。特定地域の基準①に直結します。②3町の面積及び令和2年国勢調査ベースの75歳以上人口の確定値。基準②の判定に必要です。③美瑛町の4地区（旭・北西、美馬牛、朗根内、市街地・周辺）の区域と、各事業所の「通常の事業の実施地域」。</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr"/>
+      <c r="D18" s="6" t="inlineStr"/>
+      <c r="E18" s="6" t="inlineStr"/>
+      <c r="F18" s="6" t="inlineStr"/>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>注）本報告書の各シートには、確認できた事実と、そこから導いた判断を分けて記載しています。「要確認」と付した事項は、原典の入手後に確定する必要があります。</t>
         </is>
@@ -802,7 +828,7 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A20:F20"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
@@ -816,549 +842,967 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>「中山間地域」の3つの制度概念と、大雪地区3町の該当状況</t>
+          <t>3町の地域指定（原典確認）と、特定地域（中山間・人口減少地域）の基準</t>
         </is>
       </c>
     </row>
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>「中山間地域」は制度により定義が異なる。介護分野では①介護報酬上の中山間地域等、②特別地域加算の対象地域、③第10期基本指針が用いる「中山間・人口減少地域」＝特定地域、の3つを区別する必要がある。</t>
+          <t>北海道 総合政策部地域創生局地域政策課「地域指定一覧（令和8年4月1日現在）」、国土交通省「豪雪地帯・特別豪雪地帯の指定（令和8年4月1日現在）」、第135回社会保障審議会介護保険部会 資料3「特定地域（中山間・人口減少地域）の考え方について」（令和8年6月29日）による。いずれも原典で確認済み。</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1　3つの制度概念の整理</t>
+          <t>1　3町の地域指定（原典確認済み）</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>No.</t>
+          <t>町</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>概念</t>
+          <t>過疎</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>根拠</t>
+          <t>辺地</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>山村</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>特別豪雪地帯</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>豪雪地帯／備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>豪雪地帯（道内全市町村）。特別豪雪地帯を有する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>美瑛町</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>豪雪地帯（道内全市町村）。過疎地域かつ特別豪雪地帯を有する。美瑛町過疎地域持続的発展市町村計画（令和3〜7年度）を策定している。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>東神楽町</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>豪雪地帯（道内全市町村）。特別豪雪地帯は有しない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>（参考）旭川市</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>山村は一部の区域。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>（参考）上川町</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>上川管内で最も指定が多い類型。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="52" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>注1）北海道「地域指定一覧（令和8年4月1日現在）」による。○は当該市町村が指定地域を有すること、△は市町村内の一部の区域が指定されていることを示す。注2）同一覧の凡例は『特豪』について「豪雪地帯対策特別措置法第2条第3項の規定に基づき公示された特別豪雪地帯を有する市町村（豪雪地帯：道内全市町村）」と定義しており、北海道の179市町村すべてが豪雪地帯であることが明記されている。国土交通省の指定状況でも北海道は「全域豪雪地帯（10道県）」の一つとされ、豪雪地帯179市町村・うち特別豪雪地帯86市町村と示されている。注3）『辺地』欄は「当該年度の4月1日時点において辺地総合整備計画を策定している辺地を有する市町村」を示す。3町とも該当している。注4）前回報告では東川町の特別豪雪地帯・3町の辺地を把握できていませんでした。訂正します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>2　介護報酬上の中山間地域等・特別地域への該当</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>加算</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
           <t>対象地域の要件</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>効果</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>加算率</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>3町の該当</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="110" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>確度</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="90" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>中山間地域等における小規模事業所加算</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>豪雪地帯・特別豪雪地帯／辺地／半島振興対策実施地域／特定農山村地域／過疎地域のいずれかに所在する事業所（厚生労働大臣が定める中山間地域等の地域）</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>10％</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>3町とも該当</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>高い</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>北海道全市町村が豪雪地帯であり、かつ3町とも辺地を有する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="90" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>中山間地域等に居住する者へのサービス提供加算</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>通常の事業の実施地域を越えて、上記の中山間地域等に居住する利用者にサービスを提供した場合</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>5％</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>3町とも該当</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>高い</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>同上。訪問・通所困難地域の判定材料としても使える（03シート）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="90" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>特別地域加算</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>厚生労働大臣が定める特別地域（離島振興対策実施地域、奄美群島、振興山村、小笠原諸島、沖縄の離島、特別豪雪地帯、半島振興対策実施地域、特定農山村地域、過疎地域のうち厚生労働大臣が定める地域）に所在する事業所</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>15％</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>東川町・美瑛町は該当の可能性が高い。東神楽町は該当しない可能性が高い。</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>東川町・美瑛町は特別豪雪地帯を有し、美瑛町は過疎地域でもある。ただし対象は「厚生労働大臣が定める地域」であり、特別豪雪地帯や過疎地域のすべてが対象となるわけではない。告示の確認を要する。特定地域の基準①に直結する重要な確認事項。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>3　特定地域（中山間・人口減少地域）の基準　― 3段階構造（原典 p10・p13）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>段階</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>基準</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>指定の単位</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>根拠・考え方</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>3町への適用</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23" ht="140" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>介護報酬上の「中山間地域等」</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>厚生労働大臣が定める中山間地域等の地域（平成21年3月13日厚生労働省告示第83号）</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>次のいずれかに所在すること。豪雪地帯・特別豪雪地帯／辺地／半島振興対策実施地域／特定農山村地域／過疎地域。</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>中山間地域等における小規模事業所加算（10％）／中山間地域等に居住する者へのサービス提供加算（5％）</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>3町とも該当する見込み。北海道は179市町村すべてが豪雪地帯に指定されている（令和8年4月1日現在。うち86市町村が特別豪雪地帯）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="110" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>特別地域加算・離島等相当サービスの対象地域（市町村の全部指定・一部指定いずれも含む）は、国が示す基準に含める。</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>市町村の全部又は一部</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>特定地域は「特別地域加算・離島等相当サービスの対象地域と同様の現状にある地域」が対象になるよう基準を設定するとされており、当該対象地域そのものは無条件で含まれる。</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>東川町・美瑛町が特別地域加算の対象地域であれば、①で該当する。告示の確認を要する。</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr"/>
+    </row>
+    <row r="24" ht="140" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>②</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>特別地域加算の対象地域</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>厚生労働大臣が定める特別地域（別告示）</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>離島振興対策実施地域、奄美群島、振興山村、小笠原諸島、沖縄の離島、特別豪雪地帯、半島振興対策実施地域、特定農山村地域、過疎地域のうち厚生労働大臣が定める地域。①より限定的。</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>特別地域加算（15％）</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>要確認。3町が特別豪雪地帯であるか、過疎地域である美瑛町が対象告示に掲載されているかを確認する必要がある。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="110" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>①に該当しない場合、「75歳以上人口密度＝5人／km²未満」又は「75歳以上人口＝1,000人未満かつ減少」を満たす市町村を、全域単位で指定できる。</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>市町村の全域</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>密度は特別地域加算の全域指定299市町村の中央値3.8人／km²・平均値7.2人／km²を踏まえ5人／km²。人口は同じく中央値725人・平均値1,146人を踏まえ1,000人。これに「現に需要が減少している地域を捉える観点」から減少要件を付す。該当は全国356市町村（20.5％）＝特別地域加算全域指定299＋密度基準で新たに40＋人口基準で新たに17。</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>美瑛町は密度基準に該当する見込み（下記4）。東川町・東神楽町は密度基準・人口基準とも非該当の見込み。</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr"/>
+    </row>
+    <row r="25" ht="140" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>③</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>第10期基本指針の「中山間・人口減少地域」＝特定地域</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>第135回社会保障審議会介護保険部会 資料3（令和8年6月29日）／介護保険法改正（令和9年4月1日施行予定）</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>基準素案は、特別地域加算が適用されるエリアを基本とした上で、75歳以上人口が①1km²あたり5人未満、又は②1,000人未満かつ減少している、のいずれかを満たす市町村。全国の約21％（356市町村）が全域該当となる見通し。</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>特定地域サービス（人員配置基準の緩和、出来高払いに加えた月単位の包括払いの選択）／特定地域居宅サービス等事業（地域のサービス提供主体が少ない場合に市町村が事業として居宅介護サービス等を実施できる）</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>市町村単位で判定される。下記2のとおり、美瑛町は該当が確実、東神楽町は非該当が確実、東川町は非該当だが確定値での検証を要する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>注1）①と②は介護報酬（加算）の制度であり、③は計画策定と人員基準・報酬体系の特例に関する制度です。同じ「中山間地域」という語でも対象範囲と効果が異なるため、計画本文では区別して記載する必要があります。注2）③の基準は令和8年6月29日に素案として示されたもので、告示前です。原典（第135回資料3）の文言を確認のうえ確定してください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>2　特定地域の基準を3町に当てはめた場合の判定</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>①②に該当しない場合でも、⑴市町村内の一部地域において②の基準に該当する地域、⑵特定のサービス類型の事業所が地域に存在しない、事業所が僅少かつ当該事業所が廃止を検討しているなど、現に指定サービス等を前提としたサービス基盤の維持が困難である地域（市町村の全域又は一部地域）、を指定することも可能とする。</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>市町村の全域又は一部地域（一部地域の範囲は旧市町村単位、行政区単位、日常生活圏域単位が考えられる）</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>①②の人口基準では捉えられない、サービス基盤の維持が困難な地域を個別に指定できるようにする趣旨。</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>当広域連合は全28サービス種別のうち11種別で域内事業所がゼロであり、⑵に直接該当する。①②に該当しない東川町・東神楽町についても、当該サービス類型について指定を受ける道が開かれている。また一部地域の範囲に日常生活圏域単位が明示されているため、美瑛町の朗根内地区等を圏域単位で指定することも考えられる。</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr"/>
+    </row>
+    <row r="27" ht="39" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>【重要】前回報告では基準を「特別地域加算のエリアを基本としたうえで密度・人口の要件」と説明しましたが、原典では上記のとおり3段階の構造であり、③により①②に該当しない市町村・地域も指定できることが明記されています。特に③⑵の「特定のサービス類型の事業所が地域に存在しない」は、当広域連合の11種別の空白（検証報告書21シート）にそのまま当てはまります。前回「美瑛町のみが該当」とお伝えした点を訂正します。3町とも、少なくとも事業所が存在しないサービス類型については指定の対象となり得ます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>【指定の手続】原典は「以下の基準に該当する地域について、市町村が特定地域としての指定の要否を検討し、その意向を踏まえて都道府県が対象地域を定める」としています。すなわち起点は市町村（保険者）の意向表明であり、第10期計画にその意向を記載することが実質的な入口となります。北海道との協議を第1回委員会前に開始することを推奨します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>4　基準②を3町に当てはめた場合の試算</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>町</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>面積（km²）</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>5人／km²の閾値</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>75歳以上人口（推計）</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>密度（人／km²）</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>基準①5人未満</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>判定と根拠</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="100" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>美瑛町</t>
         </is>
       </c>
-      <c r="B15" s="8" t="n">
+      <c r="B34" s="11" t="n">
         <v>676.78</v>
       </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>約2,100〜2,400人</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>3.1〜3.5</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>該当</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>面積676.78km²に対し5人／km²の閾値は3,384人。美瑛町の65歳以上人口は約3,675人（令和5年）であり、75歳以上人口が3,384人を超えることはあり得ない。したがって基準①に該当することが確実。加えて美瑛町は過疎地域に指定されており（美瑛町過疎地域持続的発展市町村計画 令和3〜7年度）、特別地域加算の対象地域である可能性もある。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="100" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>3,384人</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>約2,000〜2,100人</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>3.0〜3.1</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>基準②の密度要件に該当する見込み。閾値3,384人に対し、美瑛町の65歳以上人口が約3,675人であることを踏まえれば、75歳以上人口がこれを超えることはあり得ない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>東川町</t>
         </is>
       </c>
-      <c r="B16" s="8" t="n">
+      <c r="B35" s="11" t="n">
         <v>247.3</v>
       </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>約1,520〜1,600人</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>6.1〜6.5</t>
-        </is>
-      </c>
-      <c r="E16" s="10" t="inlineStr">
-        <is>
-          <t>非該当（要確認）</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>面積247.3km²に対し5人／km²の閾値は1,236人。推計値1,520〜1,600人はこれを約23〜29％上回るため非該当と判断される。基準②（1,000人未満かつ減少）も、人口が25年以上増加している町であり非該当。ただし閾値との差が大きくないため、確定値での検証を要する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="100" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>1,236人</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>約1,500〜1,550人</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>6.1〜6.3</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>非該当の見込み。閾値1,236人を約21〜25％上回る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>東神楽町</t>
         </is>
       </c>
-      <c r="B17" s="8" t="n">
+      <c r="B36" s="11" t="n">
         <v>68.5</v>
       </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>約1,390〜1,600人</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>20.3〜23.4</t>
-        </is>
-      </c>
-      <c r="E17" s="11" t="inlineStr">
-        <is>
-          <t>非該当</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>面積68.5km²に対し5人／km²の閾値は342人。推計値はこれを4倍以上上回るため非該当が確実。基準②も1,000人を超えており、かつ人口は増加しているため非該当。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>注1）面積は検索結果による値であり、確定値は国土地理院「全国都道府県市区町村別面積調」により確認してください。注2）75歳以上人口は、見える化A3（後期高齢者数）の大雪地区合計（令和5年5,487人・令和7年5,701人・令和8年5,748人）と、第9期計画の町別高齢化率（東川31.4％・美瑛38.8％・東神楽28.7％）及び検索結果の町別の75歳以上割合から推計した幅です。3町の年齢階級別人口の確定値による検証を要します。注3）判定は市町村単位で行われるため、大雪地区広域連合という保険者単位では判定されません。美瑛町のみが特定地域となる場合、同一保険者の区域内で人員基準・報酬体系が異なるサービスが併存することになります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>3　特定地域に該当した場合に使える制度（令和9年4月施行予定）</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>342人</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>約1,500〜1,600人</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>21.9〜23.4</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>非該当。閾値342人を4倍以上上回る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>（参考）大雪地区広域連合計</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="n">
+        <v>992.58</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>4,963人</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>5,167人（令和2年）</t>
+        </is>
+      </c>
+      <c r="E37" s="11" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>参考値。判定は市町村単位で行われるため保険者単位では判定されない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="52" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>注1）原典は密度・人口とも総務省「令和2年国勢調査」、人口変化率は同調査と社人研「日本の地域別将来推計人口 令和5(2023)年推計」による2020年→2025年の変化率としています。上表の75歳以上人口は、見える化A3の令和2年の後期高齢者数（大雪地区計5,167人）を第9期計画の町別高齢化率で按分した推計値です。3町の確定値による検証を要します。注2）基準②のもう一方の要件「75歳以上人口1,000人未満かつ減少」については、当広域連合の75歳以上人口が令和2年5,167人から令和7年5,701人へ10.3％増加しており、3町とも人口要件・減少要件のいずれも満たさないと考えられます。注3）東川町の密度は閾値との差が21〜25％であり、按分の前提により結果が変わり得ます。確定値での検証を要します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>5　特定地域に該当した場合に使える制度</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>制度</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>大雪地区での想定される活用</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>前提条件</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>留意点</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr"/>
-    </row>
-    <row r="24" ht="150" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>特定地域サービス</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>中山間・人口減少地域に限り、人員配置基準を緩和した特例的な介護サービスの類型。管理者や専門職の常勤・専従要件、夜勤要件の緩和等。報酬は従来の出来高払いに加え、月単位で定額を支払う包括払いも選択可能。</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>美瑛町において、既存事業所の人員基準を緩和することで事業継続を支援する。特に介護老人福祉施設の准看護師（7人→3人）、生活相談員（5人→3人）、機能訓練指導員（2人→1人）の減少（検証報告書22シート）への対応として有効。</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>職員の賃金の改善に向けた取組、ICT機器の活用、サービス・事業所間での連携等が前提とされている。</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>職員の負担への配慮が求められる。緩和と負担増が同時に進まないよう、労働時間・離職率の監視が必要。</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="inlineStr"/>
-    </row>
-    <row r="25" ht="150" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>内容（介護保険部会意見書・原典）</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>対象サービス</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>施行時期</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>当広域連合での想定</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr"/>
+    </row>
+    <row r="44" ht="150" customHeight="1">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>特例介護サービスの新たな類型（特定地域サービス）</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>「人材確保、ICT機器の活用等の生産性向上の方策など、自治体が必要な施策を講じた上で、それでもなおやむを得ない場合、中山間・人口減少地域に限定した特例的なサービス提供を行う枠組みとして、特例介護サービスに新たな類型を設けることが適当」。職員の賃金の改善に向けた取組、ICT機器の活用、サービス・事業所間での連携等を前提に、管理者や専門職の常勤・専従要件、夜勤要件の緩和等を行う。サービスの質の確保の観点から、市町村の適切な関与・確認や配置職員の専門性への配慮を前提とする。</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>現行の基準該当サービス・離島等相当サービスの対象となっている居宅サービス等（訪問介護、訪問入浴介護、通所介護、短期入所生活介護、福祉用具貸与、居宅介護支援等）に加え、施設サービス、特定施設入居者生活介護も対象とすることが適当。市町村が指定権者である地域密着型サービスも同様の対応を実施できるようにする。</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>令和9年4月（第10期初年度）</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>介護老人福祉施設で准看護師が7人→3人、生活相談員が5人→3人、機能訓練指導員が2人→1人へ減少している状況（検証報告書22シート）への対応となる。施設サービスも対象とされている点が当広域連合にとって重要。</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr"/>
+    </row>
+    <row r="45" ht="150" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>包括的な評価（月単位の定額払い）</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>「特例介護サービスの新たな類型の枠組みにおいて、安定的な経営を行う仕組みとして、例えば訪問介護について、現行のサービス提供回数に応じた出来高報酬と別途、包括的な評価（月単位の定額払い）を選択可能とすることが適当」。季節による繁閑が大きい地域や小規模事業所の経営安定、移動時間の考慮、突然のキャンセルによる機会損失の抑制等のメリットが挙げられている。</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>訪問介護等</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>「希望する自治体においては、第10期介護保険事業計画期間中の実施を可能とすることを目指し、第9期介護保険事業計画期間中に検討を進めることが適当」と明記されている。</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>当広域連合は訪問介護の利用回数が全国の1.87倍と突出しており、包括払いを導入した場合の影響（利用者負担、区分支給限度基準額との関係、保険料水準）の検討が必要。導入の可否は慎重に判断すべき。</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr"/>
+    </row>
+    <row r="46" ht="150" customHeight="1">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>特定地域居宅サービス等事業</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>地域のサービス提供主体が少ない場合に、市町村が事業として居宅介護サービス等を実施できる仕組み。</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>当広域連合では全28サービス種別のうち11種別で域内事業所がゼロであり（検証報告書21シート）、まさにこの制度が想定する状況にある。特に定期巡回・随時対応型訪問介護看護、看護小規模多機能型居宅介護、訪問入浴介護は、13年間にわたり事業者の参入がない。第6章第4節の24時間対応サービスの確保方策として、A案（民間による整備）・B案（旭川市の事業所の利用）・C案（既存サービスによる代替）に加えて、第4の案「D案：特定地域居宅サービス等事業として実施」を検討できる。</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>市町村（保険者）が実施主体となるため、広域連合と3町の役割分担の整理が必要。特定地域の指定を受けていることが前提となる可能性が高い。</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>美瑛町のみが特定地域となる場合、東川町・東神楽町では使えない可能性がある。制度の適用単位（市町村単位か保険者単位か）を北海道経由で確認する必要がある。</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="inlineStr"/>
-    </row>
-    <row r="27" ht="52" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>注）基本指針案は、都道府県と市町村の連携等が重要な事項の例として「中山間・人口減少地域において人材確保やICT機器の活用等の生産性向上に係る支援を行うことや、それでもなおやむを得ない場合に新たな特例介護サービスや対象地域の検討」を挙げています（第135回資料2-1）。すなわち、①まず人材確保・ICT等の支援を行い、②それでもなおやむを得ない場合に特例介護サービスを検討する、という順序が示されています。当広域連合の場合、24時間対応の3サービスは13年間にわたり事業者の参入がなく、「まず支援を行う」対象となる既存事業者自体が存在しないため、この順序をそのまま適用できるかを北海道と協議する必要があります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>4　計画本文への反映（案）</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>「給付における特例の仕組みを活用しても、なおサービス提供体制を維持することが困難なケース」に備え、「給付の仕組みに代えて、市町村が関与する事業により、給付と同様に介護保険財源を活用し、事業者がサービス提供を可能とする仕組みを設けることが適当」。</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>居宅サービス等</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>令和9年4月（制度設計は介護保険部会で継続議論）</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>11種別で事業所ゼロという状況に直接対応する。24時間対応サービスの確保方策の第4の選択肢（D案）として素案第10稿に追加済み。</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr"/>
+    </row>
+    <row r="47" ht="150" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>介護事業者の連携強化</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>地域において中心的な役割を果たす法人・事業所が、一定期間にわたり事業継続する役割を担うことや、複数の事業所間の連携促進・他法人の間接業務の引受け等を行う仕組み。法人間での人材の連携等を行う場合の配置基準の弾力化、ICT導入補助、介護報酬の加算による評価等のインセンティブ付与が検討されている。</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>検討中</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>当広域連合は事業所数が少なく（居宅介護支援10、訪問介護13）、中心的役割を担う法人の特定が比較的容易。第5章 基本目標4に位置づけを検討。</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr"/>
+    </row>
+    <row r="48" ht="150" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>既存施設の有効活用（国庫納付の特例拡充）</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>中山間・人口減少地域に所在する介護施設等について、経過年数10年未満でも福祉施設への全部転用等の際の国庫納付を不要とする等の特例を拡充。「高齢者人口の急減など、真にやむを得ない場合において、他の施設との統合等のため高齢者事業を廃止する場合は、自治体、地域の事業者・関係者・住民との合意形成を図った上で介護保険事業計画等へ位置付けることを条件に」転用等の国庫納付を不要とする。</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>法令・通知改正等により対応</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>介護老人福祉施設の定員が234人から160人へ31.6％縮小している当広域連合では、今後さらに転用・統合の判断が生じ得る。その際は計画への位置づけと合意形成が条件となるため、第6章第5節の整備方針に手順を書いておく必要がある。</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr"/>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>6　計画本文への反映</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>反映先</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>記載内容</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>根拠</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr"/>
-      <c r="E31" s="4" t="inlineStr"/>
-      <c r="F31" s="4" t="inlineStr"/>
-    </row>
-    <row r="32" ht="54" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>状況</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr"/>
+      <c r="E51" s="4" t="inlineStr"/>
+      <c r="F51" s="4" t="inlineStr"/>
+    </row>
+    <row r="52" ht="50" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>第1章第9節（制度改正）</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>第10期から中山間・人口減少地域（特定地域）に係る特例が創設されること、美瑛町が特定地域に該当する見込みであること、当該制度が令和9年4月から施行される予定であることを記載する。</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>第135回資料3、介護保険法改正</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-    </row>
-    <row r="33" ht="54" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>特定地域の3段階基準、3町の地域指定、特定地域サービス・特定地域居宅サービス等事業の創設を記載する。</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>素案第10稿に反映済み（第2版で基準の3段階構造に修正）</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr"/>
+      <c r="E52" s="6" t="inlineStr"/>
+      <c r="F52" s="6" t="inlineStr"/>
+    </row>
+    <row r="53" ht="50" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>第2章第3節（サービス提供体制）</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>3町の地域指定の状況（豪雪地帯、過疎地域等）を一覧で示し、介護報酬上の加算の対象となる区域を明示する。</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>本シート1</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-    </row>
-    <row r="34" ht="54" customHeight="1">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>第6章第4節1（24時間対応サービスの確保方策）</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>確保方策の選択肢に「D案：特定地域居宅サービス等事業として市町村が実施」を追加する。</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>本シート3</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr"/>
-      <c r="E34" s="6" t="inlineStr"/>
-      <c r="F34" s="6" t="inlineStr"/>
-    </row>
-    <row r="35" ht="54" customHeight="1">
-      <c r="A35" s="6" t="inlineStr">
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>3町の地域指定の一覧を掲載し、介護報酬上の加算の対象区域を明示する。</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>第2版で追加</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr"/>
+      <c r="E53" s="6" t="inlineStr"/>
+      <c r="F53" s="6" t="inlineStr"/>
+    </row>
+    <row r="54" ht="50" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>第6章第4節1（24時間対応の確保方策）</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>D案（特定地域居宅サービス等事業）の根拠として基準③⑵を明記する。</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>素案第10稿に反映済み（第2版で根拠を明記）</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr"/>
+      <c r="E54" s="6" t="inlineStr"/>
+      <c r="F54" s="6" t="inlineStr"/>
+    </row>
+    <row r="55" ht="50" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>第6章第5節（整備の基本方針）</t>
         </is>
       </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>特定地域サービスの活用により既存事業所の人員基準を緩和し事業継続を支援する方針を記載する。</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>本シート3</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr"/>
-      <c r="E35" s="6" t="inlineStr"/>
-      <c r="F35" s="6" t="inlineStr"/>
-    </row>
-    <row r="36" ht="54" customHeight="1">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>資料6（別表への対応）</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>別表一（地勢と交通）の対応欄に、3町の地域指定の状況を記載する。</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>本シート1</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr"/>
-      <c r="E36" s="6" t="inlineStr"/>
-      <c r="F36" s="6" t="inlineStr"/>
-    </row>
-    <row r="38" ht="39" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>【確認をお願いしたい事項】①3町の面積及び年齢階級別（5歳階級）人口の確定値。特に75歳以上人口を町別に確定する必要があります。②北海道『道内の過疎、辺地、山村、離島、特豪地帯等の指定状況（令和8年4月1日現在）』における3町の指定状況。③3町の事業所で特別地域加算・中山間地域等小規模事業所加算・中山間地域等居住者サービス提供加算を算定している事業所の有無と件数。これは実務上、当該区域が加算の対象地域であることの直接の証拠となります。④第135回資料3の原典（告示前の素案）。北海道経由での入手をご検討ください。</t>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>特定地域サービスによる人員基準の緩和、既存施設の転用時の合意形成の手順を記載する。</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>第2版で追加</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr"/>
+      <c r="E55" s="6" t="inlineStr"/>
+      <c r="F55" s="6" t="inlineStr"/>
+    </row>
+    <row r="57" ht="52" customHeight="1">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>【確認をお願いしたい事項】①特別地域加算の対象地域告示（厚生労働大臣が定める特別地域）に東川町・美瑛町が掲載されているかどうか。特定地域の基準①に直結します。北海道への照会が最も確実です。②3町の面積及び令和2年国勢調査ベースの75歳以上人口の確定値。③3町の事業所における特別地域加算・中山間地域等小規模事業所加算・中山間地域等居住者サービス提供加算の算定状況。算定していれば、当該区域が対象地域であることの実務上の証拠となります。④北海道に対し、特定地域の指定について当広域連合が意向を示す時期と手続の確認。原典は「市町村が指定の要否を検討し、その意向を踏まえて都道府県が対象地域を定める」としており、市町村側からの意向表明が起点となります。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A38:F38"/>
+  <mergeCells count="7">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A57:F57"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1370,35 +1814,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>計画の評価・共有に関する法的根拠と他団体の動向</t>
+          <t>進捗管理の手引きが示す標準手順と、府中町の自己評価シートの実例</t>
         </is>
       </c>
     </row>
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金の評価で「評価結果を関係者間で共有し、自立支援等に資する取組を検討」及び「今年度の評価得点」がいずれも0点であったことを受け、評価と共有の制度的位置づけと他団体の実装方法を調査した。</t>
+          <t>厚生労働省老健局介護保険計画課「介護保険事業（支援）計画の進捗管理の手引き」（平成30年7月30日）及び広島県府中町「取組と目標に対する自己評価シート」（令和6年度分）による。いずれも原典で確認済み。</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1　制度的位置づけ</t>
+          <t>1　手引きが示すPDCAの基本的な考え方（原典 第1部）</t>
         </is>
       </c>
     </row>
@@ -1415,339 +1859,638 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
+          <t>手引きの記載</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>当広域連合との関係</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6" ht="100" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>策定年度だけの分析にとどまっている実態</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>「これまで、自治体においては、介護保険事業（支援）計画の策定年度においてのみ、高齢者等への調査や関係者へのヒアリング等により地域の現況を把握して課題の分析を行い、取り組むべき取組を設定するにとどまっているのが一般的でした。」</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>第9期において代表KPIの検証が計画期末の1回のみであったことは、手引きが「一般的」と指摘する状態そのものである。</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr"/>
+      <c r="F6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7" ht="100" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>3年ごとのPDCAでは足りない</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>「介護保険事業（支援）計画は、3年に一度作成されるため、3年ごとのPDCAサイクルが活用されることがあります。……自治体の予算や各事業は年度ごとに配分され実施されること、進捗管理すべき内容は多岐に渡っていること、自治体の職員は定期的に人事異動によって変わってしまうことなどを考慮すると、少なくとも年度ごとのPDCAサイクルも活用すべきだと考えられます。」</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>3町との共同運営であり職員の異動もあるため、年度ごとのサイクルの必要性は当広域連合に強く当てはまる。</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr"/>
+      <c r="F7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8" ht="100" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>2つのサイクルを同時に活用する</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>「年度ごとに締めた実績を活用するPDCAサイクル」（前年度実績が6月頃確定するため6月に評価し当該年度の実施方法の改善に活かす）と、「予算要求等の事務サイクルを活用するPDCAサイクル」（9月末現在の中間実績を参考に10月に評価し次年度の改善の必要性を考察する）の「2つのサイクルには一長一短があるため、2つのサイクルを同時に活用しながら、年度ごとのPDCAサイクルも活用すべき」。</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>素案第10稿 第1章第6節の年次手順を、この2サイクル構成に合わせて修正する必要がある（第2版で修正）。</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr"/>
+    </row>
+    <row r="9" ht="100" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>評価と公表・報告</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>「市町村及び都道府県が、介護保険事業（支援）計画策定期以降に、介護保険事業（支援）計画に記載したサービス見込量や取組や目標を継続的に評価、分析し、その成果を公表するとともに、必要に応じて見直しを行うための標準的な手順や考え方を示しました。」「市町村は、これら取組と目標の達成状況を自己評価し、都道府県に報告する」。</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>評価・公表・都道府県への報告が一体で求められている。北海道への報告実績の有無が、評価を実施していたかどうかの証跡となる。</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>2　手引きが示す年度内のPDCAスケジュール（原典 図表1-1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>時期</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>手引きが示す作業</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>根拠となる実績</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>当広域連合での実施内容（案）</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>成果物</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13" ht="88" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>4〜5月</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>年度の開始。KPIの定義・対象・基準月・担当者を確定する。</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>年度実施要領を作成し、3町へ様式を配布する。</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>年度実施要領</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr"/>
+    </row>
+    <row r="14" ht="88" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>6月</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>【サイクル1】前年度の実績の自己評価。前年度の実績等が6月頃確定するため、取組や事業の達成度や進捗を評価する。</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>前年度の確定実績</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>前年度のKPI16項目の実績を算定し、達成／概ね達成／未達／評価不能を判定する。</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>年次評価スコアカード（前年度分）</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15" ht="88" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>7〜9月</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>当該年度の取組の充実。評価結果を当該年度の取組や事業の実施方法の改善等に活かす。補正予算での対応も視野に入れる。</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>介護保険事業計画策定委員会（運営協議会）へ報告し、意見を受ける。3町・事業者・関係機関へ評価結果を共有する。ホームページで公表する。</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>委員会資料、公表資料</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16" ht="88" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>10月</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>【サイクル2】当該年度の実績の自己評価。9月末現在の中間地点における実績を参考に、達成度や進捗を評価する。</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>9月末現在の中間実績</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>認定者数・給付費・受給者数の9月末値により計画乖離を点検する。見える化の9月月報値と同じ基準時点であり、整合的。</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>中間評価表</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr"/>
+    </row>
+    <row r="17" ht="88" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>11〜3月</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>次年度の取組案の充実。次年度の取組や事業の改善の必要性に気づいた場合は当初予算の計上も可能であり、抜本的な立て直しも可能。</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>次年度の事業設計と当初予算要求に反映する。改善措置の責任者と期限を決定する。</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>改善措置一覧</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr"/>
+    </row>
+    <row r="19" ht="39" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>注）素案第10稿 第1章第6節では「4月要領→7月KPI算定→9月委員会→10月共有→12月改善確認」としていましたが、手引きの2サイクル構成に合わせて上表のとおり修正します。特に、①前年度実績の確定が6月頃であること、②10月の中間評価が次年度当初予算に接続すること、の2点が重要です。10月の中間評価は9月末現在の実績を用いるため、見える化システムの認定者数の基準月（9月月報）と同じ時点となり、整合的です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>3　自己評価シートの様式（原典 第3部）と府中町の実例</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>府中町の記載内容（令和6年度・介護給付費等適正化）</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>当広域連合での記載案</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24" ht="76" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>フェイスシート</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>タイトル</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>介護保険事業の円滑な運営</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>―（基本目標ごとに1件作成する案）</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr"/>
+      <c r="F24" s="6" t="inlineStr"/>
+    </row>
+    <row r="25" ht="76" customHeight="1">
+      <c r="A25" s="6" t="inlineStr"/>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>□自立支援、介護予防、重度化防止　■介護給付費等適正化（2区分から選択）</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>法定の2区分。当広域連合も同じ2区分で最低2件を作成する。</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr"/>
+      <c r="F25" s="6" t="inlineStr"/>
+    </row>
+    <row r="26" ht="76" customHeight="1">
+      <c r="A26" s="6" t="inlineStr"/>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>現状と課題</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>「高齢化の進展に伴う介護サービスの利用者数の増加により、介護費用が増大する中、介護保険制度の信頼感を高め、持続的運営を図るため、利用者に過不足のない適切な介護サービスを提供する必要がある。」</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>第2章・第3章の分析結果をそのまま引用できる。交付金評価で推進Ⅱが全国の39.0％であることを課題として記載する。</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr"/>
+      <c r="F26" s="6" t="inlineStr"/>
+    </row>
+    <row r="27" ht="76" customHeight="1">
+      <c r="A27" s="6" t="inlineStr"/>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>具体的な取組</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>①要介護認定調査の適正化　②ケアプラン点検及び住宅改修・福祉用具点検　③縦覧点検・医療情報との突合　④サービス事業者の指導・監査</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>第5章 基本目標5(4)の主な事業をそのまま使える。当広域連合が0点である②③は、府中町が現に実施している内容である。</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr"/>
+      <c r="F27" s="6" t="inlineStr"/>
+    </row>
+    <row r="28" ht="76" customHeight="1">
+      <c r="A28" s="6" t="inlineStr"/>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>目標（事業内容、指標等）</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>取組ごとに具体的な実施方法を記載。介護予防の例では参加者数370人→385人→400人、団体数19団体→…と年度別の数値目標を掲げている。</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>第5章各基本目標(4)のアウトプット目標と(5)の達成目標をそのまま転記する。</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr"/>
+      <c r="F28" s="6" t="inlineStr"/>
+    </row>
+    <row r="29" ht="76" customHeight="1">
+      <c r="A29" s="6" t="inlineStr"/>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>目標の評価方法</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>「各取組の実績件数等で評価した。」</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>KPI定義書の算式を記載する。</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr"/>
+      <c r="F29" s="6" t="inlineStr"/>
+    </row>
+    <row r="30" ht="76" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>自己評価結果</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>実施内容</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>実施した内容を具体的に記載。</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr"/>
+      <c r="F30" s="6" t="inlineStr"/>
+    </row>
+    <row r="31" ht="76" customHeight="1">
+      <c r="A31" s="6" t="inlineStr"/>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>自己評価結果</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>【○】（◎達成できた、○概ね達成できた、△達成はやや不十分、×全く達成できなかった の4段階）</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>素案第10稿の資料3では「達成／概ね達成／未達／評価不能」の4区分としており、手引きの4段階と対応する。ただし「評価不能」は手引きにない区分であるため、データ源が確保できない指標の扱いを注記する。</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr"/>
+      <c r="F31" s="6" t="inlineStr"/>
+    </row>
+    <row r="32" ht="76" customHeight="1">
+      <c r="A32" s="6" t="inlineStr"/>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>課題と対応策</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>「■課題　地域の身近なところに通いの場の数を増やすことが必要だが、立ち上げを支援する人や世話人になる人がいない。■対応策　お元気サポーター養成講座を継続実施し……」</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>素案第10稿の資料3の「乖離要因」「改善措置」に対応する。</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr"/>
+      <c r="F32" s="6" t="inlineStr"/>
+    </row>
+    <row r="34" ht="52" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>注1）府中町は法定2区分ごとに1件ずつ、計2件のシートを作成しています。当広域連合は5基本目標であるため、基本目標ごとに1件（計5件）とするか、法定2区分に合わせて2件とするかを決める必要があります。交付金評価の得点構造（推進Ⅰ〜Ⅲ・支援Ⅰ〜Ⅲ・共通Ⅳ）との対応を考えると、基本目標ごとの5件を推奨します。注2）府中町の介護予防のシートでは、「参加人数はほぼ目標値を達成したが、週1回体操を実施する団体数が、目標の設置数には届いていない」と参加者数と団体数を分けて評価しています。当広域連合の通いの場も、参加率（1.6％）と箇所数（3箇所）を分けて評価する方針であり（素案第10稿 第5章 基本目標2）、同じ考え方です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>4　0点の要因の仮説と検証方法</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>仮説</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>当広域連合との関係</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>出典</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6" ht="90" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>介護保険法第117条による法定化</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>第7期計画から、自立支援、介護予防、重度化防止及び介護給付の適正化に係る取組と目標が計画の法定記載事項とされ、市町村はその実績に関する評価を行い、結果を都道府県へ報告するとともに、公表に努めることとされている。</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>第9期計画は代表KPI4項目を掲げているが、年次の評価と公表を行った記録が確認できない。交付金評価の「今年度の評価得点」が0点であることと整合する。</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>介護保険法第117条</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr"/>
-    </row>
-    <row r="7" ht="90" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>進捗管理の手引き</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>厚生労働省老健局介護保険計画課「介護保険事業（支援）計画の進捗管理の手引き」（平成30年7月30日）が、PDCAサイクルに沿った進捗管理の標準的な手順を示している。市町村が自己評価を行い、都道府県が評価結果をもとに取組と目標の進捗状況を確認し、市町村と支援内容に関する意見交換を行う流れとされている。</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>第10期計画の第1章第6節に年次の進行管理の手順を新設した（素案第10稿）。手引きの手順と整合しているかを確認する必要がある。</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>厚生労働省老健局介護保険計画課（平成30年7月30日）</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr"/>
-    </row>
-    <row r="8" ht="90" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>交付金の評価項目</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>市町村介護保険事業計画を策定する際に、保険者機能強化推進交付金等の評価結果を活用して市町村の実情及び地域課題を分析することが求められている。評価結果を関係者間で共有し、自立支援・重度化防止等に関する施策の遂行に活用することが評価指標として設定されている。</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>当広域連合はこの項目が0点（全国平均8.1点）。「評価を行っていない」のか「評価は行ったが共有の記録がない」のかを評価調書で判別する必要がある。</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>保険者機能強化推進交付金 評価指標（市町村分）</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr"/>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>2　他団体の実装方法</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>区分</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>団体・区分</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>実装の内容</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>当広域連合への適用可能性</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>出典</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12" ht="100" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>公表の方法</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>広島県府中町</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>平成30年度（第7期計画初年度）以降の自己評価結果をホームページに継続して掲載している。</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>最も簡素な実装。年次のスコアカードをそのままホームページに掲載すれば、「評価を行い公表している」ことの証跡となる。第10期の資料3（年次評価スコアカード）をそのまま公表資料とすることを推奨する。</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>府中町公式サイト</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr"/>
-    </row>
-    <row r="13" ht="100" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>KPIの年次管理</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>大阪府堺市ほか</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>年齢別要介護認定率、リハビリ教室の利用者数、リハビリ加算の算定事業所数等の複数のKPIについて、実績値と目標値を年度ごとに管理・公表している。</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>当広域連合の第10期は代表KPI16項目を設定しており、実績値と目標値を年度ごとに並べた一覧を作成すれば同等の実装となる。アウトカム指標だけでなく、アウトプット指標（第5章の各基本目標(4)）も同じ表で管理することを推奨する。</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>第8期高齢者かがやきプラン等</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr"/>
-    </row>
-    <row r="14" ht="100" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>交付金評価のKPI化</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>島根県（都道府県）</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>保険者機能強化推進交付金の評価指数が全国平均値を上回る市町村数を、都道府県計画のKPIとして設定している。</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>当広域連合は1保険者であるため「市町村数」は使えないが、「交付金の総合得点が全国平均以上」を保険者自身のKPIとすることは可能。素案第10稿の基本目標5の達成目標に同趣旨の指標を設定済み（基準値332.0点→目標「全国平均以上」）。</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>島根創生計画</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr"/>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>3　0点の要因の仮説と検証方法</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>仮説</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>検証方法</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>該当した場合の対応</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18" ht="70" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="E38" s="4" t="inlineStr"/>
+      <c r="F38" s="4" t="inlineStr"/>
+    </row>
+    <row r="39" ht="80" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>A　評価そのものを行っていない</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>第9期計画の代表KPI4項目について、年度ごとの実績算定を行っていない。本検証で令和8年3月末実績を初めて算定したことと整合する。</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>令和6年度・令和7年度の評価資料（庁内・委員会向けを含む）の有無を確認する。</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>第10期から年次評価を開始する。素案第10稿 第1章第6節の手順による。</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr"/>
-      <c r="F18" s="6" t="inlineStr"/>
-    </row>
-    <row r="19" ht="70" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>第9期計画の代表KPI4項目について、年度ごとの実績算定を行っていない。本検証で令和8年3月末実績を初めて算定したことと整合する。手引きが「策定年度においてのみ……にとどまっているのが一般的」と指摘する状態。</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>令和6年度・令和7年度の評価資料（庁内・委員会向けを含む）の有無を確認する。あわせて北海道への報告実績の有無を確認する。</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>第10期から年次評価を開始する。手引きの様式（自己評価シート）をそのまま用いる。</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr"/>
+      <c r="F39" s="6" t="inlineStr"/>
+    </row>
+    <row r="40" ht="80" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>B　評価は行ったが公表・共有の記録がない</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>内部では実績を把握していたが、委員会への報告、3町・事業者への共有、ホームページでの公表の記録がない。</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>運営協議会・委員会の議事録、3町への通知文書の有無を確認する。</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>評価の実施自体は継続し、共有と公表の手順のみを追加する。年次評価スコアカードの公表で足りる。</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-    </row>
-    <row r="20" ht="70" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>評価の実施自体は継続し、共有と公表の手順のみを追加する。府中町のように自己評価シートをホームページに掲載すれば足りる。</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr"/>
+      <c r="F40" s="6" t="inlineStr"/>
+    </row>
+    <row r="41" ht="80" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>C　評価調書の記載方法の問題</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>実際には評価・共有を行っていたが、交付金の評価調書で要件を満たす形で記載できていなかった。</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>令和4〜6年度の評価調書の当該項目の回答内容を確認する。</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>評価調書の記載方法を見直す。取組の内容は変えずに得点が改善する。</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr"/>
-    </row>
-    <row r="22" ht="39" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>【確認をお願いしたい事項】①令和4〜6年度の保険者機能強化推進交付金の評価調書のうち、推進Ⅰ「評価結果を関係者間で共有し、自立支援等に資する取組を検討しているか」及び「今年度の評価得点」の項目の回答内容。②第9期計画の代表KPIについて、令和6年度・令和7年度に実績を算定した資料の有無。③介護保険運営協議会（又は策定委員会）に計画の進捗を報告した実績の有無と、その議事録。④自己評価結果を都道府県（北海道）へ報告した実績の有無。介護保険法第117条に基づく法定の報告であり、報告していれば評価の実施を裏付ける証跡となります。</t>
+      <c r="E41" s="6" t="inlineStr"/>
+      <c r="F41" s="6" t="inlineStr"/>
+    </row>
+    <row r="43" ht="52" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>【確認をお願いしたい事項】①令和4〜6年度の保険者機能強化推進交付金の評価調書のうち、推進Ⅰ「評価結果を関係者間で共有し、自立支援等に資する取組を検討しているか」及び「今年度の評価得点」の項目の回答内容。②第9期計画の代表KPIについて、令和6年度・令和7年度に実績を算定した資料の有無。③介護保険運営協議会（又は策定委員会）に計画の進捗を報告した実績と、その議事録。④自己評価結果を北海道へ報告した実績の有無。手引きは「市町村は、これら取組と目標の達成状況を自己評価し、都道府県に報告する」としており、報告していれば評価の実施を裏付ける証跡となります。⑤自己評価シートを基本目標ごとに5件作成するか、法定2区分に合わせて2件とするかの方針。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="5">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A43:F43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1759,7 +2502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1961,354 +2704,501 @@
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2　美瑛町の4地区の状況と暫定判定</t>
+          <t>2　美瑛町の交通の実態（美瑛町過疎地域持続的発展市町村計画・原典）</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>原典の記載</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>訪問・通所困難地域の判定への意味</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16" ht="96" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>鉄道</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>「ＪＲ富良野線が美瑛－旭川間1日19往復、美瑛－富良野間1日12往復運行しており、町内には美瑛、美馬牛、北美瑛の3駅がある。」</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>鉄道駅があるのは市街地・周辺地区（美瑛駅・北美瑛駅）と美馬牛地区（美馬牛駅）。朗根内地区・旭・北西地区には鉄道駅がない。</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr"/>
+      <c r="E16" s="6" t="inlineStr"/>
+      <c r="F16" s="6" t="inlineStr"/>
+    </row>
+    <row r="17" ht="96" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>民間バス</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>「白金温泉－美瑛－旭川間を民間バスが運行しており、ＪＲ及び民間バス交通は、住民の通勤、通学等、地域生活における貴重な交通手段となっている。」</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>民間バスの路線は白金温泉－美瑛－旭川の1系統のみ。朗根内地区・旭・北西地区・美馬牛地区は経路上にない。</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr"/>
+      <c r="E17" s="6" t="inlineStr"/>
+      <c r="F17" s="6" t="inlineStr"/>
+    </row>
+    <row r="18" ht="96" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>路線バスの廃止と代替</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>「町内には、国鉄バスの路線廃止により、昭和60年から8路線でスクールバスの運行が開始され、平成23年からは、地域の利便性を図ることを目的に、10路線が運行されている。今日では、学校の統廃合による児童生徒の遠距離通学、高齢者の通院や日常の買い物など交通弱者の貴重な公共交通として、スクールバスは欠くことのできない交通手段となっている。」</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>決定的な記載。市街地・周辺地区以外の集落には定期路線バスがなく、スクールバスが高齢者の通院・買物の唯一の公共交通となっている。町自身が「交通弱者の貴重な公共交通」と位置づけている。</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr"/>
+      <c r="E18" s="6" t="inlineStr"/>
+      <c r="F18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19" ht="96" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>朗根内地区の交通需要</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>スクールバス路線別乗車人員のうち、俵真布線（美瑛〜朗根内〜俵真布）は平成30年度7,554人、令和元年度7,453人、令和2年度8,188人で10路線中最多。</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>朗根内地区を含む路線の乗車人員が最も多い。人口233人の地区としては相当の交通需要があり、かつ他の交通手段がないことを示している。</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr"/>
+      <c r="E19" s="6" t="inlineStr"/>
+      <c r="F19" s="6" t="inlineStr"/>
+    </row>
+    <row r="20" ht="96" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>冬期の除雪</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>「道道7路線99.8kmで除雪率88％、町道414路線346.6kmで除雪率52.9％となり目標の60％に近づいている。また、歩道除雪については、51路線39.60kmで除雪率51.0％。」</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>町道の約半分（47.1％）は除雪されない。集落と市街地を結ぶ道路が町道である場合、冬期のアクセスが制約される。訪問系サービスの提供可否に直接影響する。</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr"/>
+      <c r="E20" s="6" t="inlineStr"/>
+      <c r="F20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21" ht="96" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>今後の方針</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>「引き続き、きめ細かな移動需要に対応するため、走行距離や耐用年数に応じたスクールバスの計画的な更新、デマンド型交通を含めた輸送サービスの充実を図る必要がある。」「町民の重要な交通手段であるスクールバスの計画的な整備や更新を行い、安定的な公共交通機関の確保に努める。」</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>美瑛町自身がデマンド型交通の導入を課題として掲げている。第10期計画の移動支援施策（第5章 基本目標2）と接続できる。</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr"/>
+      <c r="E21" s="6" t="inlineStr"/>
+      <c r="F21" s="6" t="inlineStr"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>3　美瑛町の4地区の状況と判定</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
           <t>地区</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>人口</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>高齢者人口</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>高齢化率</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>交通</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>暫定判定と根拠</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="76" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>判定と根拠</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="84" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>市街地・周辺地区</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B25" s="13" t="inlineStr">
         <is>
           <t>7,869人</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C25" s="13" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D25" s="13" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>JR富良野線 美瑛駅。道北バス（旭川・白金温泉方面）。</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>ＪＲ美瑛駅・北美瑛駅。民間バス（旭川・白金温泉方面）。</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <t>非該当。町の中心部であり、事業所も集中していると考えられる。</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="76" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="26" ht="84" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>美馬牛地区</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>［要確認］</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>［要確認］</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>［要確認］</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>ＪＲ美馬牛駅。スクールバス美馬牛線（美瑛〜美馬牛。令和2年度2,408人）。</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>要確認。鉄道駅があるため公共交通の面では条件が良い。ただし駅から離れた集落は町道の除雪率52.9％の影響を受ける可能性がある。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="84" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>旭・北西地区</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B27" s="13" t="inlineStr">
         <is>
           <t>684人</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C27" s="13" t="inlineStr">
         <is>
           <t>308人</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D27" s="13" t="inlineStr">
         <is>
           <t>45.0％</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>［要確認］</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>要確認。高齢化率45.0％は4地区で最も高い。美瑛駅からの距離と冬期の道路状況の確認を要する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="76" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>美馬牛地区</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>［要確認］</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>［要確認］</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>［要確認］</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>JR富良野線 美馬牛駅がある。</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>要確認。鉄道駅があるため公共交通の面では条件が良いが、訪問系サービスの提供地域に含まれるかは別に確認を要する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="76" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>鉄道駅・民間バスなし。スクールバス旭線（美瑛〜北瑛〜旭。令和2年度4,612人）。</t>
+        </is>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>該当の可能性がある。高齢化率45.0％は4地区で最も高い。定期路線バスがなくスクールバスが唯一の公共交通。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="84" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>朗根内地区</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B28" s="13" t="inlineStr">
         <is>
           <t>233人</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C28" s="13" t="inlineStr">
         <is>
           <t>82人</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>［要確認］</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>鉄道駅なし。定期路線バスの有無は［要確認］。</t>
-        </is>
-      </c>
-      <c r="F19" s="12" t="inlineStr">
-        <is>
-          <t>該当の可能性が高い。人口233人は最大の市街地・周辺地区の33.8分の1であり、この規模の集落に訪問系事業所が通常の事業の実施地域を設定しているとは考えにくい。最優先で確認すべき地区。</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="39" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>注1）人口・高齢者人口は第9期計画 第1章第7節の掲載値です。注2）美瑛町の面積は676.78km²で、3町の中で最も広く、東神楽町（68.5km²）の約9.9倍です。同じ町内でも移動距離が大きく異なります。注3）東川町・東神楽町については、第9期計画が各1圏域としているため地区別のデータがありません。東川町は大雪山国立公園を含み面積247.3km²であり、山間部に訪問・通所困難地域が存在する可能性があります。旭岳温泉地区等の状況の確認を提案します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>鉄道駅・民間バスなし。スクールバス俵真布線（美瑛〜朗根内〜俵真布。令和2年度8,188人・10路線中最多）。</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>該当の可能性が最も高い。定期路線バスがなく、人口233人は最大の市街地・周辺地区の33.8分の1。この規模の集落に訪問系事業所が通常の事業の実施地域を設定しているとは考えにくい。最優先で確認すべき地区。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="52" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>注1）人口・高齢者人口は第9期計画 第1章第7節の掲載値、交通は美瑛町過疎地域持続的発展市町村計画（令和3〜7年度）の記載によります。注2）美瑛町の面積は676.78km²で、3町の中で最も広く、東神楽町（68.5km²）の約9.9倍です。注3）東川町・東神楽町については、第9期計画が各1圏域としているため地区別のデータがありません。東川町は大雪山国立公園を含み面積247.3km²であり、旭岳温泉地区等の山間部の状況の確認を提案します。注4）特定地域の基準③は一部地域の指定を認めており、その範囲として「旧市町村単位、行政区単位、日常生活圏域単位」が挙げられています（01シート）。訪問・通所困難地域として特定した地区を、そのまま特定地域として指定することを検討できます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>3　確認の手順（提案）</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>段階</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>作業</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>実施主体</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>成果物</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E34" s="4" t="inlineStr">
         <is>
           <t>時期</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr"/>
-    </row>
-    <row r="26" ht="64" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="F34" s="4" t="inlineStr"/>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>第1段階</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>3町及び北海道から、区域内で訪問介護・訪問看護・通所介護・地域密着型通所介護・通所リハビリテーションを提供する全事業所の運営規程における「通常の事業の実施地域」を収集する。</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>受託者（広域連合・北海道経由）</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>事業所別の実施地域一覧</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E35" s="6" t="inlineStr">
         <is>
           <t>現状分析前</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr"/>
-    </row>
-    <row r="27" ht="64" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="F35" s="6" t="inlineStr"/>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>第2段階</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>美瑛町4地区・東川町・東神楽町の各区域について、いずれの事業所の実施地域にも含まれない区域を特定する。</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>訪問・通所困難地域の候補一覧</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E36" s="6" t="inlineStr">
         <is>
           <t>現状分析前</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr"/>
-    </row>
-    <row r="28" ht="64" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="F36" s="6" t="inlineStr"/>
+    </row>
+    <row r="37" ht="64" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>第3段階</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>候補地区について、中山間地域等居住者サービス提供加算の算定実績、冬期の道路状況、公共交通の状況を確認する。</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>受託者・3町</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>地区別の状況整理表</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E37" s="6" t="inlineStr">
         <is>
           <t>第1回委員会前</t>
         </is>
       </c>
-      <c r="F28" s="6" t="inlineStr"/>
-    </row>
-    <row r="29" ht="64" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="F37" s="6" t="inlineStr"/>
+    </row>
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>第4段階</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>訪問・通所困難地域を確定し、当該地域へのアクセスと社会資源の状況を第1章第7節（日常生活圏域）及び第2章第3節（サービス提供体制）に記載する。</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>計画本文への反映</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="E38" s="6" t="inlineStr">
         <is>
           <t>第2回委員会前</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr"/>
-    </row>
-    <row r="30" ht="64" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="F38" s="6" t="inlineStr"/>
+    </row>
+    <row r="39" ht="64" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>第5段階</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>確定した困難地域に対する施策（移動支援、送迎の広域化、特定地域居宅サービス等事業の活用等）を第5章 基本目標3に位置づける。</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t>受託者・広域連合・3町</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t>施策案</t>
         </is>
       </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="E39" s="6" t="inlineStr">
         <is>
           <t>第2回委員会前</t>
         </is>
       </c>
-      <c r="F30" s="6" t="inlineStr"/>
-    </row>
-    <row r="32" ht="39" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="F39" s="6" t="inlineStr"/>
+    </row>
+    <row r="41" ht="39" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>【確認をお願いしたい事項】①区域内で訪問系・通所系サービスを提供する全事業所の運営規程における「通常の事業の実施地域」（地域密着型は広域連合が保有、居宅サービスは北海道が保有）。②中山間地域等居住者サービス提供加算及び特別地域加算の算定事業所と算定件数。③美瑛町の4地区の区域図と、地区別の人口・高齢者人口（美馬牛地区の数値が第9期計画にない）。④東川町の旭岳温泉地区等、山間部の居住状況。⑤3町の除雪計画における優先路線と、冬期の通行支障の実績。</t>
         </is>
@@ -2316,11 +3206,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="A41:F41"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A30:F30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3065,7 +3955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3282,12 +4172,12 @@
     <row r="16" ht="100" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>特定地域サービス（特例介護サービスの新類型）</t>
+          <t>特定地域の基準③⑵（事業所が存在しない地域の指定）</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>中山間・人口減少地域に限り、人員配置基準を緩和した特例的な介護サービスの類型。報酬は出来高払いに加え、月単位の包括払いを選択可能。</t>
+          <t>「特定のサービス類型の事業所が地域に存在しない、事業所が僅少かつ当該事業所が廃止を検討しているなど、現に指定サービス等を前提としたサービス基盤の維持が困難である地域（市町村の全域又は一部地域）」を特定地域として指定することも可能とする。</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -3297,12 +4187,12 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>美瑛町が特定地域に該当する見込み（01シート）。既存事業所の事業継続支援に使える。</t>
+          <t>当広域連合の11種別の空白がそのまま該当する。①②の人口基準に該当しない東川町・東神楽町についても、当該サービス類型について指定の道が開かれている。計画に指定の意向を記載することが実質的な入口となる。</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>第135回介護保険部会 資料3ほか</t>
+          <t>第135回介護保険部会 資料3 p10（原典確認済み）</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr"/>
@@ -3310,27 +4200,27 @@
     <row r="17" ht="100" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>特定地域居宅サービス等事業</t>
+          <t>特例介護サービスの新類型（特定地域サービス）</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>地域のサービス提供主体が少ない場合に、市町村が事業として居宅介護サービス等を実施できる仕組み。</t>
+          <t>人材確保、ICT機器の活用等の生産性向上の方策など自治体が必要な施策を講じた上で、それでもなおやむを得ない場合に、中山間・人口減少地域に限定した特例的なサービス提供を行う枠組み。管理者や専門職の常勤・専従要件、夜勤要件の緩和等。対象は現行の基準該当・離島等相当サービスの対象サービスに加え、施設サービス、特定施設入居者生活介護、地域密着型サービスも含むことが適当とされている。</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月1日</t>
+          <t>令和9年4月1日（詳細要件は介護給付費分科会で議論）</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>11種別で事業所ゼロという当広域連合の状況に直接対応する制度。24時間対応サービスの確保方策の第4の選択肢となる。</t>
+          <t>既存事業所の事業継続支援に使える。施設サービスも対象とされている点が、介護老人福祉施設の職種別人員が減少している当広域連合にとって重要。</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>第135回介護保険部会 資料3 p14（原典確認済み）</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr"/>
@@ -3338,27 +4228,27 @@
     <row r="18" ht="100" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>基本指針案の記載（真にやむを得ない場合の廃止・転用）</t>
+          <t>包括的な評価（月単位の定額払い）</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>「特に中山間・人口減少地域において、真にやむを得ない場合における高齢者事業の廃止・転用等について記載」（第二 市町村計画 2 各年度における介護給付等対象サービスの種類ごとの見込量の確保のための方策）。</t>
+          <t>訪問介護等について、現行のサービス提供回数に応じた出来高報酬と別途、包括的な評価（月単位の定額払い）を選択可能とする。「希望する自治体においては、第10期介護保険事業計画期間中の実施を可能とすることを目指し、第9期介護保険事業計画期間中に検討を進めることが適当」とされている。</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>第10期計画から</t>
+          <t>第10期計画期間中（第9期中に検討）</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>サービスを整備しないという判断も、計画に明示的に記載すべき事項として位置づけられている。「事業所がないから書かない」のではなく、「整備しない理由と代替方策」を書くことが求められる。</t>
+          <t>当広域連合は訪問介護の利用回数が全国の1.87倍と突出しており、包括払い導入時の利用者負担・区分支給限度基準額・保険料水準への影響の検討が必要。</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>第135回介護保険部会 資料2-1 p62</t>
+          <t>第135回介護保険部会 資料3 p15（原典確認済み）</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr"/>
@@ -3366,27 +4256,27 @@
     <row r="19" ht="100" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>基本指針案の記載（新たな特例介護サービスの関係者意見）</t>
+          <t>特定地域居宅サービス等事業</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>「新たな特例介護サービスについて関係者の意見を聞くことの重要性について記載」（p63）。</t>
+          <t>「給付における特例の仕組みを活用しても、なおサービス提供体制を維持することが困難なケース」に備え、給付の仕組みに代えて、市町村が関与する事業により、給付と同様に介護保険財源を活用し、事業者がサービス提供を可能とする仕組み。</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>第10期計画から</t>
+          <t>令和9年4月1日（制度設計は介護保険部会で継続議論）</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>特例介護サービスの導入を検討する場合、事業者・利用者・医療関係者の意見聴取が前提となる。</t>
+          <t>11種別で事業所ゼロという当広域連合の状況に直接対応する制度。24時間対応サービスの確保方策の第4の選択肢となる。</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>同上 p63</t>
+          <t>第135回介護保険部会 資料3 p16（原典確認済み）</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr"/>
@@ -3394,233 +4284,233 @@
     <row r="20" ht="100" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
+          <t>基本指針案の記載（真にやむを得ない場合の廃止・転用）</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>「特に中山間・人口減少地域において、真にやむを得ない場合における高齢者事業の廃止・転用等について記載」（第二 市町村計画 2 各年度における介護給付等対象サービスの種類ごとの見込量の確保のための方策）。</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>第10期計画から</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>サービスを整備しないという判断も、計画に明示的に記載すべき事項として位置づけられている。「事業所がないから書かない」のではなく、「整備しない理由と代替方策」を書くことが求められる。</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>第135回介護保険部会 資料2-1 p62</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21" ht="100" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>基本指針案の記載（新たな特例介護サービスの関係者意見）</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>「新たな特例介護サービスについて関係者の意見を聞くことの重要性について記載」（p63）。</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>第10期計画から</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>特例介護サービスの導入を検討する場合、事業者・利用者・医療関係者の意見聴取が前提となる。</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>同上 p63</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22" ht="100" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
           <t>基本指針案の記載（都道府県との連携）</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>「中山間・人口減少地域において人材確保やICT機器の活用等の生産性向上に係る支援を行うことや、それでもなおやむを得ない場合に新たな特例介護サービスや対象地域の検討」を都道府県と市町村の連携が重要な事項の例として明記。</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>第10期計画から</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>①まず人材確保・ICT等の支援、②それでもやむを得ない場合に特例、という順序。当広域連合の24時間対応3サービスは事業者自体が存在せず「まず支援する対象」がないため、この順序の適用を北海道と協議する必要がある。</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>同上 第二4／第三4</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr"/>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>3　北海道の動向</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>事項</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>当広域連合との関係</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr"/>
-      <c r="E23" s="4" t="inlineStr"/>
-      <c r="F23" s="4" t="inlineStr"/>
-    </row>
-    <row r="24" ht="104" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>圏域単位の調整・協議の場</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>基本指針案は「地域の状況に応じ順次、介護保険事業計画について老人福祉圏域単位等で調整・協議するための会議体を設置するなど、地域における2040年に向けたサービス提供の在り方について、本格的に議論するための体制を構築することが適当」としている。</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>上川中部高齢者保健福祉圏域（旭川市ほか10市町村）での協議の場が設置される可能性がある。定期巡回は圏域全体では令和8年に68.0人／月、看多機は101.0人／月の見込みがあり、当広域連合だけが空白であることを圏域の場で議題にできる。</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr"/>
-      <c r="E24" s="6" t="inlineStr"/>
-      <c r="F24" s="6" t="inlineStr"/>
-    </row>
-    <row r="25" ht="104" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>市町村計画の共同作成への支援</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>「複数の市町村が市町村介護保険事業計画の共同作成に取り組む場合に、都道府県が支援を行うことの必要性について記載」（第三 都道府県計画）。</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>当広域連合は既に3町共同の保険者であるが、3町の高齢者福祉計画との整合について北海道の支援を求める根拠となる。</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
+      <c r="D25" s="4" t="inlineStr"/>
+      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr"/>
     </row>
     <row r="26" ht="104" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>第9期北海道計画における記載</t>
+          <t>圏域単位の調整・協議の場</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>北海道第9期計画 第7章第12節（上川中部圏域）は、圏域の定期巡回・随時対応型訪問介護看護をR4実績59.1人／月→R8 68.0人／月、看護小規模多機能型居宅介護をR4実績1.0人／月→R6 64.0人／月→R8 101.0人／月と見込んでいる。</t>
+          <t>基本指針案は「地域の状況に応じ順次、介護保険事業計画について老人福祉圏域単位等で調整・協議するための会議体を設置するなど、地域における2040年に向けたサービス提供の在り方について、本格的に議論するための体制を構築することが適当」としている。</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>北海道は圏域として当該サービスの拡大を見込んでおり、当広域連合がゼロのままであることは道計画との不整合となる。第10期北海道計画の策定過程で協議すべき事項。</t>
+          <t>上川中部高齢者保健福祉圏域（旭川市ほか10市町村）での協議の場が設置される可能性がある。定期巡回は圏域全体では令和8年に68.0人／月、看多機は101.0人／月の見込みがあり、当広域連合だけが空白であることを圏域の場で議題にできる。</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr"/>
       <c r="E26" s="6" t="inlineStr"/>
       <c r="F26" s="6" t="inlineStr"/>
     </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
+    <row r="27" ht="104" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>市町村計画の共同作成への支援</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>「複数の市町村が市町村介護保険事業計画の共同作成に取り組む場合に、都道府県が支援を行うことの必要性について記載」（第三 都道府県計画）。</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>当広域連合は既に3町共同の保険者であるが、3町の高齢者福祉計画との整合について北海道の支援を求める根拠となる。</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr"/>
+      <c r="E27" s="6" t="inlineStr"/>
+      <c r="F27" s="6" t="inlineStr"/>
+    </row>
+    <row r="28" ht="104" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>第9期北海道計画における記載</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>北海道第9期計画 第7章第12節（上川中部圏域）は、圏域の定期巡回・随時対応型訪問介護看護をR4実績59.1人／月→R8 68.0人／月、看護小規模多機能型居宅介護をR4実績1.0人／月→R6 64.0人／月→R8 101.0人／月と見込んでいる。</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>北海道は圏域として当該サービスの拡大を見込んでおり、当広域連合がゼロのままであることは道計画との不整合となる。第10期北海道計画の策定過程で協議すべき事項。</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr"/>
+      <c r="E28" s="6" t="inlineStr"/>
+      <c r="F28" s="6" t="inlineStr"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>4　当広域連合の11種別の扱い方針（提案）</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>サービス</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>第10期の扱い</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>見込量</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>計画本文の記載</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr"/>
-    </row>
-    <row r="30" ht="110" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>A　確保方策を決定する</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>定期巡回・随時対応型訪問介護看護、看護小規模多機能型居宅介護</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>第6章第4節1で確保方策（A〜D案）を決定する。整備・広域利用のいずれかを選ぶ場合は見込量を計上する。</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>確保方策に応じて設定。整備する場合はガイドp89・p90の手順で利用者数と給付費（全国平均値等を参考）を直接入力する。</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>第2章第3節（空白の事実）、第6章第4節1（確保方策）、第5章 基本目標3（施策）に記載する。</t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="inlineStr"/>
-    </row>
-    <row r="31" ht="110" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>B　代替により対応する</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>夜間対応型訪問介護、訪問入浴介護</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>整備しない。代替方策（訪問介護・訪問看護の組合せ、区域外事業所の利用）を明示する。</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>ゼロのまま（訪問入浴は区域外事業所により給付があるため実績を計上）。</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>基本指針案が求める「真にやむを得ない場合における廃止・転用等」に準じ、整備しない理由と代替方策を第6章第5節に記載する。</t>
-        </is>
-      </c>
-      <c r="F31" s="6" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr"/>
     </row>
     <row r="32" ht="110" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>C　区域外の事業所により充足している</t>
+          <t>A　確保方策を決定する</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>福祉用具貸与、認知症対応型通所介護、介護医療院、短期入所療養介護（病院等）、同（介護医療院）</t>
+          <t>定期巡回・随時対応型訪問介護看護、看護小規模多機能型居宅介護</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>整備しない。区域外事業所による給付で足りているかを自給率（国保連の給付実績情報）で確認する。</t>
+          <t>第6章第4節1で確保方策（A〜D案）を決定する。整備・広域利用のいずれかを選ぶ場合は見込量を計上する。</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>実績（区域外事業所による給付）に基づき計上する。</t>
+          <t>確保方策に応じて設定。整備する場合はガイドp89・p90の手順で利用者数と給付費（全国平均値等を参考）を直接入力する。</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節に「事業所がないことと給付がないことは別である」旨を注記する（素案第10稿に記載済み）。</t>
+          <t>第2章第3節（空白の事実）、第6章第4節1（確保方策）、第5章 基本目標3（施策）に記載する。</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr"/>
@@ -3628,33 +4518,89 @@
     <row r="33" ht="110" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
+          <t>B　代替により対応する</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>夜間対応型訪問介護、訪問入浴介護</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>整備しない。代替方策（訪問介護・訪問看護の組合せ、区域外事業所の利用）を明示する。</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>ゼロのまま（訪問入浴は区域外事業所により給付があるため実績を計上）。</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>基本指針案が求める「真にやむを得ない場合における廃止・転用等」に準じ、整備しない理由と代替方策を第6章第5節に記載する。</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr"/>
+    </row>
+    <row r="34" ht="110" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>C　区域外の事業所により充足している</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>福祉用具貸与、認知症対応型通所介護、介護医療院、短期入所療養介護（病院等）、同（介護医療院）</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>整備しない。区域外事業所による給付で足りているかを自給率（国保連の給付実績情報）で確認する。</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>実績（区域外事業所による給付）に基づき計上する。</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>第2章第3節に「事業所がないことと給付がないことは別である」旨を注記する（素案第10稿に記載済み）。</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr"/>
+    </row>
+    <row r="35" ht="110" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
           <t>D　制度上廃止・全国的にも僅少</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>介護療養型医療施設、地域密着型特定施設入居者生活介護</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>整備しない。介護療養型は令和6年度に制度上廃止。</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>ゼロ。</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="E35" s="6" t="inlineStr">
         <is>
           <t>制度上の理由を注記するにとどめる。</t>
         </is>
       </c>
-      <c r="F33" s="6" t="inlineStr"/>
-    </row>
-    <row r="35" ht="52" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
+      <c r="F35" s="6" t="inlineStr"/>
+    </row>
+    <row r="37" ht="52" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>【確認をお願いしたい事項】①第10期の見込量において、定期巡回・随時対応型訪問介護看護及び看護小規模多機能型居宅介護を計上するかどうかの方針。計上する場合、ガイドp89・p90の手順で利用者数と1人1月あたり給付費を直接入力します。給付費は全国平均値の使用が明示的に認められています。②特定地域居宅サービス等事業（令和9年4月施行予定）の適用可否について、北海道への照会。特に、①適用単位が市町村か保険者か、②特定地域の指定を受けていることが前提か、の2点。③上川中部圏域における協議の場の設置予定の有無。④北海道が第10期支援計画で圏域の定期巡回・看多機をどう見込むかの方向性。</t>
         </is>
@@ -3665,7 +4611,7 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A37:F37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4469,4 +5415,597 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>第1版（検索結果に依拠）から第2版（原典確認）への訂正一覧</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>令和8年7月29日に発注者から原典5点の提供を受け、全事項を原典で検証した。第1版の記載を訂正した箇所は次のとおり。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>1　訂正した事項</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>事項</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>第1版の記載（検索結果による）</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>第2版の記載（原典確認）</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>訂正の重要度</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>原典</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="118" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>特定地域の基準の構造</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>「特別地域加算が適用されるエリアを基本とした上で、75歳以上人口が①1km²あたり5人未満、又は②1,000人未満かつ減少を満たす市町村」と2要素の並列として説明していた。</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>3段階の構造。①特別地域加算・離島等相当サービスの対象地域は無条件で含まれる。②これに該当しない市町村は密度・人口の基準で全域指定できる。③①②に該当しない場合でも、一部地域が②の基準に該当する地域や、特定のサービス類型の事業所が地域に存在しない地域を指定できる。</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>重大</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>第135回資料3 p10・p13</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="118" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>3町の特定地域該当の見通し</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>「美瑛町は該当が確実、東神楽町は非該当が確実、東川町は非該当だが要確認」として、美瑛町のみが該当し得ると説明していた。</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>基準③⑵により、3町とも事業所が存在しないサービス類型について指定の対象となり得る。美瑛町は基準②の密度要件にも該当する見込み。東川町・美瑛町は基準①（特別地域加算の対象地域）に該当する可能性もある。</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>重大</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>第135回資料3 p10</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="118" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>3町の地域指定</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>「北海道は179市町村すべてが豪雪地帯」「美瑛町は過疎地域」までは把握していたが、東川町の特別豪雪地帯及び3町の辺地は把握していなかった。</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>東川町＝辺地・特別豪雪地帯、美瑛町＝過疎・辺地・特別豪雪地帯、東神楽町＝辺地。3町とも辺地を有し、東川町・美瑛町は特別豪雪地帯を有する。</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>重要</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>北海道 地域指定一覧（R8.4.1現在）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="118" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>年次評価の手順</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>素案第10稿 第1章第6節に「4月要領→7月KPI算定→9月委員会→10月共有→12月改善確認」の手順を記載していた。</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>手引きは2つのサイクルの同時活用を求めている。①前年度実績（6月頃確定）による6月の自己評価と当該年度の改善、②9月末現在の中間実績による10月の自己評価と次年度当初予算への反映。この構成に修正した。</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>重要</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>進捗管理の手引き 図表1-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="118" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>美瑛町の交通の実態</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>「朗根内地区は鉄道駅・定期路線バスがなく、該当の可能性が高い」と推定していた。</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>美瑛町過疎地域持続的発展市町村計画が「国鉄バスの路線廃止により昭和60年からスクールバスの運行が開始され」「高齢者の通院や日常の買い物など交通弱者の貴重な公共交通として、スクールバスは欠くことのできない交通手段」と明記。俵真布線（美瑛〜朗根内〜俵真布）の乗車人員は10路線中最多。町道414路線346.6kmの除雪率は52.9％。</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>補強（推定が原典で裏付けられた）</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>美瑛町過疎地域持続的発展市町村計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="118" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>他団体の自己評価の実装</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>「府中町が自己評価結果をホームページに掲載している」という事実のみ把握していた。</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>府中町のシートは手引きの様式そのもの（フェイスシート＋各年度の自己評価結果）であり、法定2区分ごとに1件ずつ作成している。給付適正化では認定調査の適正化・ケアプラン点検・縦覧点検と医療情報との突合・事業者指導の4本立てで、当広域連合が0点である項目を現に実施している。</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>補強</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>府中町 自己評価シート（R6年度）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2　第1版で用いた二次情報の扱い</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>第2版での扱い</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr"/>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15" ht="76" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>報道記事等の二次情報</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>第1版では、外部接続の制限により原典を確認できなかったため、報道記事及び業界紙の記述を出典として示していました。</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>すべて原典（第135回資料3）に差し替え、二次情報の引用は削除しました。本報告書及び計画本文で引用する出典は、国・都道府県・市町村の公表資料に限定します。</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr"/>
+      <c r="E15" s="6" t="inlineStr"/>
+      <c r="F15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16" ht="76" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>検索結果の要約</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>第1版では、3町の面積・75歳以上人口の割合等を検索結果の要約から引用していました。</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>面積は引き続き検索結果由来の値であり、国土地理院「全国都道府県市区町村別面積調」による確認を要します。75歳以上人口は見える化A3（後期高齢者数）の保険者計を第9期計画の町別高齢化率で按分した推計値であることを明記しました。</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr"/>
+      <c r="E16" s="6" t="inlineStr"/>
+      <c r="F16" s="6" t="inlineStr"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>3　第2版で確定した事項と、なお確認を要する事項</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>事項</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr"/>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20" ht="40" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>確定</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>3町の地域指定（過疎・辺地・山村・離島・半島・特豪）</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>北海道の地域指定一覧（令和8年4月1日現在）で確定。</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr"/>
+      <c r="E20" s="6" t="inlineStr"/>
+      <c r="F20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21" ht="40" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>確定</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>北海道179市町村すべてが豪雪地帯であること</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>国土交通省の指定状況及び北海道の地域指定一覧の凡例で確定。</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr"/>
+      <c r="E21" s="6" t="inlineStr"/>
+      <c r="F21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>確定</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>特定地域の3段階基準と、事業所が存在しない地域の指定（基準③⑵）</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>第135回資料3 p10で確定。</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr"/>
+      <c r="E22" s="6" t="inlineStr"/>
+      <c r="F22" s="6" t="inlineStr"/>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>確定</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>特定地域サービスの対象サービスに施設サービス・特定施設入居者生活介護・地域密着型サービスが含まれること</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>第135回資料3 p14（介護保険部会意見書抜粋）で確定。</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr"/>
+      <c r="E23" s="6" t="inlineStr"/>
+      <c r="F23" s="6" t="inlineStr"/>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>確定</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>包括的な評価（月単位の定額払い）を第10期計画期間中に実施可能とする方針</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>第135回資料3 p15で確定。</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr"/>
+      <c r="E24" s="6" t="inlineStr"/>
+      <c r="F24" s="6" t="inlineStr"/>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>確定</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>年度内PDCAの2サイクル構成</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>進捗管理の手引き 図表1-1で確定。</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr"/>
+      <c r="E25" s="6" t="inlineStr"/>
+      <c r="F25" s="6" t="inlineStr"/>
+    </row>
+    <row r="26" ht="40" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>確定</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>美瑛町の集落に定期路線バスがなくスクールバスが代替していること</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>美瑛町過疎地域持続的発展市町村計画で確定。</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr"/>
+      <c r="E26" s="6" t="inlineStr"/>
+      <c r="F26" s="6" t="inlineStr"/>
+    </row>
+    <row r="27" ht="40" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>特別地域加算の対象地域告示に東川町・美瑛町が掲載されているか</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>特定地域の基準①に直結。北海道への照会が確実。</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr"/>
+      <c r="E27" s="6" t="inlineStr"/>
+      <c r="F27" s="6" t="inlineStr"/>
+    </row>
+    <row r="28" ht="40" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>3町の面積及び令和2年国勢調査ベースの75歳以上人口の確定値</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>基準②の判定に必要。特に東川町は閾値との差が21〜25％と大きくない。</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr"/>
+      <c r="E28" s="6" t="inlineStr"/>
+      <c r="F28" s="6" t="inlineStr"/>
+    </row>
+    <row r="29" ht="40" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>各事業所の「通常の事業の実施地域」</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>訪問・通所困難地域の確定に必要。居宅サービスは北海道、地域密着型は広域連合が保有。</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr"/>
+      <c r="E29" s="6" t="inlineStr"/>
+      <c r="F29" s="6" t="inlineStr"/>
+    </row>
+    <row r="30" ht="40" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>交付金の評価調書の当該項目の回答内容</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>0点の要因（仮説A・B・C）の判別に必要。</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr"/>
+      <c r="E30" s="6" t="inlineStr"/>
+      <c r="F30" s="6" t="inlineStr"/>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>注）原典5点のご提供により、6件の照会事項のうち5件について確度が「原典確認済み」となりました。残る1件（北海道の指標の読替えに関する他団体の事例）は、外部接続の制限により事例の特定ができていません。北海道が管内の広域連合に読替えの考え方を示している可能性があるため、北海道への照会をご検討ください。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A32:F32"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/output/第10期計画_追加調査報告書.xlsx
+++ b/output/第10期計画_追加調査報告書.xlsx
@@ -1619,7 +1619,7 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>11種別で事業所ゼロという状況に直接対応する。24時間対応サービスの確保方策の第4の選択肢（D案）として素案第10稿に追加済み。</t>
+          <t>11種別で事業所ゼロという状況に直接対応する。24時間対応サービスの確保方策の第4の選択肢（D案）として計画素案に追加済み。</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr"/>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>素案第10稿に反映済み（第2版で基準の3段階構造に修正）</t>
+          <t>計画素案に反映済み（第2版で基準の3段階構造に修正）</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr"/>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>素案第10稿に反映済み（第2版で根拠を明記）</t>
+          <t>計画素案に反映済み（第2版で根拠を明記）</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr"/>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>素案第10稿 第1章第6節の年次手順を、この2サイクル構成に合わせて修正する必要がある（第2版で修正）。</t>
+          <t>計画素案 第1章第6節の年次手順を、この2サイクル構成に合わせて修正する必要がある（第2版で修正）。</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr"/>
@@ -2144,7 +2144,7 @@
     <row r="19" ht="39" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>注）素案第10稿 第1章第6節では「4月要領→7月KPI算定→9月委員会→10月共有→12月改善確認」としていましたが、手引きの2サイクル構成に合わせて上表のとおり修正します。特に、①前年度実績の確定が6月頃であること、②10月の中間評価が次年度当初予算に接続すること、の2点が重要です。10月の中間評価は9月末現在の実績を用いるため、見える化システムの認定者数の基準月（9月月報）と同じ時点となり、整合的です。</t>
+          <t>注）計画素案 第1章第6節では「4月要領→7月KPI算定→9月委員会→10月共有→12月改善確認」としていましたが、手引きの2サイクル構成に合わせて上表のとおり修正します。特に、①前年度実績の確定が6月頃であること、②10月の中間評価が次年度当初予算に接続すること、の2点が重要です。10月の中間評価は9月末現在の実績を用いるため、見える化システムの認定者数の基準月（9月月報）と同じ時点となり、整合的です。</t>
         </is>
       </c>
     </row>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>素案第10稿の資料3では「達成／概ね達成／未達／評価不能」の4区分としており、手引きの4段階と対応する。ただし「評価不能」は手引きにない区分であるため、データ源が確保できない指標の扱いを注記する。</t>
+          <t>計画素案の資料3では「達成／概ね達成／未達／評価不能」の4区分としており、手引きの4段階と対応する。ただし「評価不能」は手引きにない区分であるため、データ源が確保できない指標の扱いを注記する。</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr"/>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>素案第10稿の資料3の「乖離要因」「改善措置」に対応する。</t>
+          <t>計画素案の資料3の「乖離要因」「改善措置」に対応する。</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr"/>
@@ -2370,7 +2370,7 @@
     <row r="34" ht="52" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>注1）府中町は法定2区分ごとに1件ずつ、計2件のシートを作成しています。当広域連合は5基本目標であるため、基本目標ごとに1件（計5件）とするか、法定2区分に合わせて2件とするかを決める必要があります。交付金評価の得点構造（推進Ⅰ〜Ⅲ・支援Ⅰ〜Ⅲ・共通Ⅳ）との対応を考えると、基本目標ごとの5件を推奨します。注2）府中町の介護予防のシートでは、「参加人数はほぼ目標値を達成したが、週1回体操を実施する団体数が、目標の設置数には届いていない」と参加者数と団体数を分けて評価しています。当広域連合の通いの場も、参加率（1.6％）と箇所数（3箇所）を分けて評価する方針であり（素案第10稿 第5章 基本目標2）、同じ考え方です。</t>
+          <t>注1）府中町は法定2区分ごとに1件ずつ、計2件のシートを作成しています。当広域連合は5基本目標であるため、基本目標ごとに1件（計5件）とするか、法定2区分に合わせて2件とするかを決める必要があります。交付金評価の得点構造（推進Ⅰ〜Ⅲ・支援Ⅰ〜Ⅲ・共通Ⅳ）との対応を考えると、基本目標ごとの5件を推奨します。注2）府中町の介護予防のシートでは、「参加人数はほぼ目標値を達成したが、週1回体操を実施する団体数が、目標の設置数には届いていない」と参加者数と団体数を分けて評価しています。当広域連合の通いの場も、参加率（1.6％）と箇所数（3箇所）を分けて評価する方針であり（計画素案 第5章 基本目標2）、同じ考え方です。</t>
         </is>
       </c>
     </row>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の代表KPI4項目について、年度ごとの実績算定を行っていない。本検証で令和8年3月末実績を初めて算定したことと整合する。手引きが「策定年度においてのみ……にとどまっているのが一般的」と指摘する状態。</t>
+          <t>第9期計画の代表KPI4項目について、年度ごとの実績算定を行っていない。本検証で令和8年3月末実績を初めて算定したことと符合する。手引きが「策定年度においてのみ……にとどまっているのが一般的」と指摘する状態。</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>北海道の指標自体が率。第10期のH14として採用する（素案第10稿 第4章第3節）。</t>
+          <t>北海道の指標自体が率。第10期のH14として採用する（計画素案 第4章第3節）。</t>
         </is>
       </c>
     </row>
@@ -3935,7 +3935,7 @@
     <row r="32" ht="39" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>【提案】北海道の指標の読替えについては、単一の方式を全指標に適用するのではなく、指標の性質に応じて②と③を使い分けることを推奨します。①（日常生活圏域数）は、圏域の人口規模の偏りが解消されない限り採用しないことを推奨します。この方針は第1回介護保険事業計画策定委員会での決定事項とし、決定内容を素案第10稿 第1章第8節の注記に反映します。なお、他団体（他の広域連合）における読替えの事例は、本セッションの外部接続の制限により特定できませんでした。北海道が管内の広域連合（道内24広域連合）に対して読替えの考え方を示している可能性があるため、北海道への照会をご検討ください。</t>
+          <t>【提案】北海道の指標の読替えについては、単一の方式を全指標に適用するのではなく、指標の性質に応じて②と③を使い分けることを推奨します。①（日常生活圏域数）は、圏域の人口規模の偏りが解消されない限り採用しないことを推奨します。この方針は第1回介護保険事業計画策定委員会での決定事項とし、決定内容を計画素案 第1章第8節の注記に反映します。なお、他団体（他の広域連合）における読替えの事例は、本セッションの外部接続の制限により特定できませんでした。北海道が管内の広域連合（道内24広域連合）に対して読替えの考え方を示している可能性があるため、北海道への照会をご検討ください。</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節に「事業所がないことと給付がないことは別である」旨を注記する（素案第10稿に記載済み）。</t>
+          <t>第2章第3節に「事業所がないことと給付がないことは別である」旨を注記する（計画素案に記載済み）。</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr"/>
@@ -4798,7 +4798,7 @@
     <row r="11" ht="52" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>【当広域連合への適用】第9期計画の人口・高齢化率は住民基本台帳（各年10月1日現在）によるもので、東川町の将来推計は社人研推計を令和22年で18.5％、令和32年で21.5％上回っていました。第10期では社人研推計（見える化の初期値）に統一する方針を素案第10稿に記載していますが、ガイドの建付け上、これは「補正しない（初期値をそのまま使う）」という選択に当たります。東川町が25年以上人口増を続けている実態を推計に反映したい場合は、3町の総合計画等による推計人口を入力値として差し替えることになります。その場合、①差替えの根拠（3町の総合計画の推計値）、②社人研推計との差、③差が生じる理由（社会増の見込み）を計画本文に明記する必要があります。</t>
+          <t>【当広域連合への適用】第9期計画の人口・高齢化率は住民基本台帳（各年10月1日現在）によるもので、東川町の将来推計は社人研推計を令和22年で18.5％、令和32年で21.5％上回っていました。第10期では社人研推計（見える化の初期値）に統一する方針を計画素案に記載していますが、ガイドの建付け上、これは「補正しない（初期値をそのまま使う）」という選択に当たります。東川町が25年以上人口増を続けている実態を推計に反映したい場合は、3町の総合計画等による推計人口を入力値として差し替えることになります。その場合、①差替えの根拠（3町の総合計画の推計値）、②社人研推計との差、③差が生じる理由（社会増の見込み）を計画本文に明記する必要があります。</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>社人研推計をそのまま使う方針（素案第10稿）。東川町の社会増を織り込む場合は差替えを検討する。</t>
+          <t>社人研推計をそのまま使う方針（計画素案）。東川町の社会増を織り込む場合は差替えを検討する。</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>本検証で、粗認定率は上昇しているが年齢階級別では低下していること、性年齢調整済み要介護2以上は上昇していることを確認した（素案第10稿 第2章第1節3）。自然体推計の傾きが実態と合うかを検証したうえで補正する。</t>
+          <t>本検証で、粗認定率は上昇しているが年齢階級別では低下していること、性年齢調整済み要介護2以上は上昇していることを確認した（計画素案 第2章第1節3）。自然体推計の傾きが実態と合うかを検証したうえで補正する。</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -5321,7 +5321,7 @@
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>素案第10稿 第2章第1節3</t>
+          <t>計画素案 第2章第1節3</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr"/>
@@ -5596,7 +5596,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>素案第10稿 第1章第6節に「4月要領→7月KPI算定→9月委員会→10月共有→12月改善確認」の手順を記載していた。</t>
+          <t>計画素案 第1章第6節に「4月要領→7月KPI算定→9月委員会→10月共有→12月改善確認」の手順を記載していた。</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
